--- a/Upper Level BCIO/inputs/BCIO_Upper_Defs.xlsx
+++ b/Upper Level BCIO/inputs/BCIO_Upper_Defs.xlsx
@@ -456,92 +456,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>BFO entity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Definition source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Informal definition</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Logical definition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Synonyms</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Definition source</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'has process part'</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'realises'</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Sub-ontology</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Curator note</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'has process part'</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'realises'</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fuzzy set</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Why fuzzy</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curation status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>To be reviewed by</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Reviewer query</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Sub-ontology</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Examples</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Informal definition</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Logical definition</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>BFO entity</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Curator</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fuzzy set</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Why fuzzy</t>
         </is>
       </c>
     </row>
@@ -568,50 +568,50 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>An attribute of a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>behaviour change intervention attribute</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>An attribute of a behaviour change intervention.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -634,48 +634,48 @@
           <t>information content entity</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>A criterion for selecting people for a BCI population.</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>A criterion for selecting people for a BCI population.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>RW; JH</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -700,13 +700,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>BCI</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>BCI</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>behaviour change intervention content; participant engagement with behaviour change intervention; behaviour change intervention mechanism of action; behaviour change intervention outcome behaviour</t>
@@ -717,41 +721,37 @@
           <t>behaviour change intervention scenario plan</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Involves use of products, services, activities, rules or environmental objects.</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="n"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>JH; BG; PS</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -776,50 +776,50 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>BCI comparison evaluation study</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>BCI comparison evaluation study</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Comparison involves identifying differences between the entities in the scenarios.</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n"/>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -844,50 +844,50 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>BCI content</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BCI content</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consists of BCTs that can be classified using a BCT taxonomy. </t>
         </is>
       </c>
-      <c r="Q6" s="2" t="n"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -912,50 +912,50 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCI context</t>
+          <t>object aggregate</t>
         </is>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BCI context</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Includes as part BCI population and BCI setting. Use of the word ‘may’ conveys a non-zero probability given available information.</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>object aggregate</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n"/>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -980,46 +980,46 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCI delivery</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BCI delivery</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1044,54 +1044,54 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCI dose</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">This class requires further specification when it is used because specific BCI content instances may vary in amount in different ways. </t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BCI dose</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t xml:space="preserve">This class requires further specification when it is used because specific BCI content instances may vary in amount in different ways. </t>
         </is>
       </c>
       <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">The dose of an active ingredient in a pharmacological intervention; the number of behaviour change techniques included in an intervention. </t>
         </is>
       </c>
-      <c r="Q9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n"/>
+      <c r="U9" s="2" t="n"/>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1116,50 +1116,50 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BCI effect estimate</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BCI effect estimate</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>This includes the following subclasses: 1) BCI effect estimate type -the type of statistic used to represent the difference (e.g. odds ratio, mean difference), 2) BCI effect estimate value – the datum that represents the difference (e.g. 1.35), 3)  BCI effect estimate uncertainty type – the type of statistic used to represent the range of uncertainty of the value (e.g. 95% confidence interval see STATO), and 4) the BCI effect estimate uncertainty value  - the datum representing the uncertainty (e.g. 1.20-1.55).</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>JH; RW; BG</t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1184,46 +1184,46 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>BCI evaluation finding</t>
+          <t>information content entoty</t>
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>BCI evaluation finding</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>information content entoty</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="n"/>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>JH; RW; BG</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1248,50 +1248,50 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>BCI evaluation report</t>
+          <t>generally dependent continuant</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>BCI evaluation report</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>Includes entities that stand in direct relation to the study e.g. authors, findings, funding, aims.</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>generally dependent continuant</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1316,46 +1316,46 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>BCI evaluation study</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>BCI evaluation study</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n"/>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1380,46 +1380,46 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>BCI evaluation study plan</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>BCI evaluation study plan</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1444,46 +1444,46 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>BCI evaluation study risk of bias or error</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>BCI evaluation study risk of bias or error</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="n"/>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1508,46 +1508,46 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>BCI mechanism of action; MOA; BCI MOA</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>BCI mechanism of action; MOA; BCI MOA</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>PS; JH; RW</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1572,46 +1572,46 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>BCI mode of delivery; BCI MOD; MOD</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>BCI mode of delivery; BCI MOD; MOD</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1637,41 +1637,41 @@
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>'human behaviour' AND 'intervention outcome'</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>'human behaviour' AND 'intervention outcome'</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="n"/>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>JH; BG; PS</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1696,50 +1696,50 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BCI outcome estimate</t>
+          <t>information content entoty</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>BCI outcome estimate</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
           <t>This includes as subclasses 1) type of outcome estimate (e.g. mean, percentage), 2) value of outcome estimate (e.g. 1.5 cigs per day, 23%), 3) uncertainty estimate type (e.g. 95% CI), and 4) uncertainty estimate value (e.g. 12.0%-45.0%).</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>information content entoty</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="n"/>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1762,44 +1762,44 @@
           <t>environmental system</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>BCI physical setting</t>
-        </is>
-      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>BCI physical setting</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1822,44 +1822,44 @@
           <t>intervention population</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>BCI population</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>BCI population</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="n"/>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>JH; RW; PS</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1882,48 +1882,48 @@
           <t>planned process</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>BCI scenario</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>BCI scenario</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>behaviour change intervention outcome behaviour</t>
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
-      <c r="Q22" s="2" t="n"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="n"/>
-      <c r="T22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n"/>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1946,44 +1946,44 @@
           <t>plan</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>BCI scenario plan</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>BCI scenario plan</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n"/>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2006,44 +2006,44 @@
           <t>report</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>BCI scenario report</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>BCI scenario report</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="n"/>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2066,48 +2066,48 @@
           <t>BCI attribute</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>BCI schedule of delivery</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>BCI schedule of delivery</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
           <t>Includes the start and end of the BCI and its parts.</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="n"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2130,48 +2130,48 @@
           <t>object aggregate</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>BCI setting</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>BCI setting</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
           <t>Includes as parts social setting and physical setting.</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="n"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
-      <c r="T26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2194,44 +2194,44 @@
           <t>human population</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>BCI social setting</t>
-        </is>
-      </c>
+      <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>BCI social setting</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="n"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="n"/>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2254,48 +2254,48 @@
           <t>role</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>BCI source</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>BCI source</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
           <t>This includes individual people, groups of people, and organisations.</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="n"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2318,48 +2318,48 @@
           <t>role</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>BCI study investigator</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>BCI study investigator</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">What counts as substantively is subject to judgement. The level and nature of the contribution can be defined using the CReDiT taxonomy (https://casrai.org/credit/). </t>
         </is>
       </c>
-      <c r="Q29" s="2" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="n"/>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2382,44 +2382,44 @@
           <t>research study sample</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>BCI study sample</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>BCI study sample</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>JH; RW; PS</t>
         </is>
       </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2442,48 +2442,48 @@
           <t>communication style</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>BCI style of delivery</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>BCI style of delivery</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
           <t>An example is cold and distant vs. warm and accepting.</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="n"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R31" s="2" t="n"/>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="n"/>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2506,33 +2506,33 @@
           <t>BCI attribute</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>An attribute of a behaviour change intervention (BCI) or a BCI component whereby its content or delivery is varied according to characteristics of members of the target population or setting.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>BCI tailoring</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Tailoring can be static (i.e., conducted before intervention delivery in a case case), or dynamic (i.e., conducted one or more times after the intervention has started in a given case based on population or setting characteristics present at that time. Population and setting characteristics include the historical factors such as prior exposure to the intervention.</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Tailoring can be static (i.e., conducted before intervention delivery in a case case), or dynamic (i.e., conducted one or more times after the intervention has started in a given case based on population or setting characteristics present at that time. Population and setting characteristics include the historical factors such as prior exposure to the intervention.</t>
         </is>
       </c>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t>Tailoring the dose of pharmacotherapy for smoking cessation to the prior level of nicotine dependence of the smoker (static) or to the smokers' current strength of urges to smoke during a quit attempt (dynamic).</t>
@@ -2540,22 +2540,22 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>An attribute of a behaviour change intervention (BCI) or a BCI component whereby its content or delivery is varied according to characteristics of members of the target population or setting.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2578,44 +2578,44 @@
           <t>intervention temporal context</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>BCI temporal context</t>
-        </is>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>BCI temporal context</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
-      <c r="Q33" s="2" t="n"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2638,44 +2638,44 @@
           <t>behaviour change intervention temporal context</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>BCI temporal context event</t>
-        </is>
-      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>BCI temporal context event</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2698,44 +2698,44 @@
           <t>planned process</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>BCT</t>
-        </is>
-      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>BCT</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
-      <c r="Q35" s="2" t="n"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n"/>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>JH; RW; PS</t>
         </is>
       </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2765,33 +2765,33 @@
       <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
-      <c r="Q36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>JH; PS</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2821,33 +2821,33 @@
       <c r="I37" s="2" t="n"/>
       <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="n"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="n"/>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="n"/>
+      <c r="U37" s="2" t="n"/>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2877,33 +2877,33 @@
       <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
-      <c r="T38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="n"/>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2929,41 +2929,41 @@
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>High cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="inlineStr">
         <is>
+          <t>High cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" s="3" t="n"/>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2989,41 +2989,41 @@
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>High emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="inlineStr">
         <is>
+          <t>High emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n"/>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n"/>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="inlineStr">
+      <c r="T40" s="3" t="n"/>
+      <c r="U40" s="3" t="n"/>
+      <c r="V40" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3049,41 +3049,41 @@
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>High mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="inlineStr">
         <is>
+          <t>High mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n"/>
+      <c r="P41" s="3" t="n"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" s="3" t="inlineStr">
+      <c r="T41" s="3" t="n"/>
+      <c r="U41" s="3" t="n"/>
+      <c r="V41" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -3109,41 +3109,41 @@
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>High physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="inlineStr">
         <is>
+          <t>High physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what high exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n"/>
+      <c r="P42" s="3" t="n"/>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="inlineStr">
+      <c r="T42" s="3" t="n"/>
+      <c r="U42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A process that is an individual human behaviour or a population behaviour.</t>
+          <t>A process that is an individual human behaviour or a population behaviour. 1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3169,41 +3169,41 @@
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>"individual human behaviour" OR "population behaviour"</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
-      <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>"individual human behaviour" OR "population behaviour"</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="n"/>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>BG; PS</t>
         </is>
       </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3233,33 +3233,33 @@
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
-      <c r="Q44" s="2" t="n"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="inlineStr">
         <is>
           <t>JH; AW</t>
         </is>
       </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3289,33 +3289,33 @@
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="n"/>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3338,48 +3338,48 @@
           <t>bodily process</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>human behaviour</t>
-        </is>
-      </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>human behaviour</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
           <t>Also referred to in definitions as human behaviour or just behaviour.</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="n"/>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3409,37 +3409,37 @@
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
           <t>Examples of interventions are putting health warnings on cigarette packets, providing free stop smoking services and banning smoking in public places.</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="n"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R47" s="2" t="n"/>
-      <c r="S47" s="2" t="n"/>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="n"/>
+      <c r="U47" s="2" t="n"/>
+      <c r="V47" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U47" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3469,33 +3469,33 @@
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="n"/>
-      <c r="Q48" s="2" t="n"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R48" s="2" t="n"/>
-      <c r="S48" s="2" t="n"/>
-      <c r="T48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="n"/>
+      <c r="U48" s="2" t="n"/>
+      <c r="V48" s="2" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3513,13 +3513,13 @@
           <t>process context</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>External</t>
         </is>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3550,33 +3550,33 @@
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="n"/>
-      <c r="Q50" s="2" t="n"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R50" s="2" t="n"/>
-      <c r="S50" s="2" t="n"/>
-      <c r="T50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="n"/>
+      <c r="U50" s="2" t="n"/>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>RW</t>
         </is>
       </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3606,33 +3606,33 @@
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
-      <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n"/>
-      <c r="Q51" s="2" t="n"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R51" s="2" t="n"/>
-      <c r="S51" s="2" t="n"/>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="n"/>
+      <c r="U51" s="2" t="n"/>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3662,37 +3662,37 @@
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Includes individual human behaviour, mental activity and physiological activity. Also includes undesirable outcomes, such as treatment side effects, and unintended negative consequences of the intervention. </t>
         </is>
       </c>
-      <c r="Q52" s="2" t="n"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R52" s="2" t="n"/>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="2" t="inlineStr">
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="n"/>
+      <c r="U52" s="2" t="n"/>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3722,33 +3722,33 @@
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R53" s="2" t="n"/>
-      <c r="S53" s="2" t="n"/>
-      <c r="T53" s="2" t="inlineStr">
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="n"/>
+      <c r="U53" s="2" t="n"/>
+      <c r="V53" s="2" t="inlineStr">
         <is>
           <t>AW; PS</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3766,13 +3766,13 @@
           <t>intervention context</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>External</t>
         </is>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3799,41 +3799,41 @@
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>Low cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="n"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
+          <t>Low cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="n"/>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n"/>
+      <c r="P55" s="3" t="n"/>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="n"/>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n"/>
-      <c r="Q55" s="3" t="n"/>
-      <c r="R55" s="3" t="n"/>
-      <c r="S55" s="3" t="n"/>
-      <c r="T55" s="3" t="inlineStr">
+      <c r="T55" s="3" t="n"/>
+      <c r="U55" s="3" t="n"/>
+      <c r="V55" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U55" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3859,41 +3859,41 @@
       <c r="E56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>Low emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="n"/>
       <c r="L56" s="3" t="inlineStr">
         <is>
+          <t>Low emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="n"/>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n"/>
+      <c r="P56" s="3" t="n"/>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="n"/>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n"/>
-      <c r="Q56" s="3" t="n"/>
-      <c r="R56" s="3" t="n"/>
-      <c r="S56" s="3" t="n"/>
-      <c r="T56" s="3" t="inlineStr">
+      <c r="T56" s="3" t="n"/>
+      <c r="U56" s="3" t="n"/>
+      <c r="V56" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U56" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -3919,41 +3919,41 @@
       <c r="E57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>Low mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="n"/>
       <c r="L57" s="3" t="inlineStr">
         <is>
+          <t>Low mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="n"/>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="3" t="n"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="n"/>
+      <c r="S57" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n"/>
-      <c r="Q57" s="3" t="n"/>
-      <c r="R57" s="3" t="n"/>
-      <c r="S57" s="3" t="n"/>
-      <c r="T57" s="3" t="inlineStr">
+      <c r="T57" s="3" t="n"/>
+      <c r="U57" s="3" t="n"/>
+      <c r="V57" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U57" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -3979,41 +3979,41 @@
       <c r="E58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means </t>
-        </is>
-      </c>
+      <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="n"/>
       <c r="L58" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Low physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what low exertion means </t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="n"/>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n"/>
+      <c r="P58" s="3" t="n"/>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="n"/>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="3" t="n"/>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n"/>
-      <c r="Q58" s="3" t="n"/>
-      <c r="R58" s="3" t="n"/>
-      <c r="S58" s="3" t="n"/>
-      <c r="T58" s="3" t="inlineStr">
+      <c r="T58" s="3" t="n"/>
+      <c r="U58" s="3" t="n"/>
+      <c r="V58" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U58" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -4039,41 +4039,41 @@
       <c r="E59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>Moderate cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="n"/>
       <c r="L59" s="3" t="inlineStr">
         <is>
+          <t>Moderate cognitive exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="n"/>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="n"/>
+      <c r="P59" s="3" t="n"/>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="n"/>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n"/>
-      <c r="Q59" s="3" t="n"/>
-      <c r="R59" s="3" t="n"/>
-      <c r="S59" s="3" t="n"/>
-      <c r="T59" s="3" t="inlineStr">
+      <c r="T59" s="3" t="n"/>
+      <c r="U59" s="3" t="n"/>
+      <c r="V59" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U59" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -4099,41 +4099,41 @@
       <c r="E60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>Moderate emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="n"/>
       <c r="L60" s="3" t="inlineStr">
         <is>
+          <t>Moderate emotional management exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="n"/>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="n"/>
+      <c r="P60" s="3" t="n"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="n"/>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n"/>
-      <c r="Q60" s="3" t="n"/>
-      <c r="R60" s="3" t="n"/>
-      <c r="S60" s="3" t="n"/>
-      <c r="T60" s="3" t="inlineStr">
+      <c r="T60" s="3" t="n"/>
+      <c r="U60" s="3" t="n"/>
+      <c r="V60" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U60" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4159,41 +4159,41 @@
       <c r="E61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>Moderate mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="n"/>
       <c r="L61" s="3" t="inlineStr">
         <is>
+          <t>Moderate mental exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="n"/>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n"/>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="n"/>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="3" t="n"/>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n"/>
-      <c r="Q61" s="3" t="n"/>
-      <c r="R61" s="3" t="n"/>
-      <c r="S61" s="3" t="n"/>
-      <c r="T61" s="3" t="inlineStr">
+      <c r="T61" s="3" t="n"/>
+      <c r="U61" s="3" t="n"/>
+      <c r="V61" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U61" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -4219,41 +4219,41 @@
       <c r="E62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>Moderate physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
-        </is>
-      </c>
+      <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="n"/>
       <c r="L62" s="3" t="inlineStr">
         <is>
+          <t>Moderate physical exertion will mean different things depending on how this concept is operationalised. Therefore, when using this class, you would need to operationalise it for the relevant context (e.g., specify what moderate exertion means based on the measurement you use).</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>behaviour</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="3" t="n"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="n"/>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>behaviour</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n"/>
-      <c r="Q62" s="3" t="n"/>
-      <c r="R62" s="3" t="n"/>
-      <c r="S62" s="3" t="n"/>
-      <c r="T62" s="3" t="inlineStr">
+      <c r="T62" s="3" t="n"/>
+      <c r="U62" s="3" t="n"/>
+      <c r="V62" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U62" s="3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="V62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4278,50 +4278,50 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>BCI engagement</t>
+          <t>process</t>
         </is>
       </c>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>BCI engagement</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
           <t>Includes mental activities and behaviours.</t>
         </is>
       </c>
-      <c r="Q63" s="2" t="n"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="n"/>
+      <c r="U63" s="2" t="n"/>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>JH; RW; PS</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4346,40 +4346,40 @@
       </c>
       <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>The extend to someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>The extend to someone interacts with an intervention, including their cognitive, emotional and behavioural response (e.g., attending intervention session) to the intervention itself.</t>
-        </is>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="R64" s="2" t="n"/>
-      <c r="S64" s="2" t="n"/>
-      <c r="T64" s="2" t="inlineStr">
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="n"/>
+      <c r="U64" s="2" t="n"/>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4402,44 +4402,44 @@
           <t>process</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>human behaviour</t>
-        </is>
-      </c>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>human behaviour</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="n"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R65" s="2" t="n"/>
-      <c r="S65" s="2" t="n"/>
-      <c r="T65" s="2" t="inlineStr">
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="n"/>
+      <c r="U65" s="2" t="n"/>
+      <c r="V65" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4464,23 +4464,23 @@
       </c>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>An attribute of a process.</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="n"/>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
           <t>This is intended to provide a user-friendly way of representing the way in which processes are manifest. This is somewhat similar to, but not the same as, the class 'specifically dependent continuant' in Basic Formal Ontology which provides a way of representing features of material entities such as age and size. It is formally equivalent to process profile in Basic Formal Ontology.</t>
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>An attribute of a process.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R66" s="2" t="n"/>
-      <c r="S66" s="2" t="n"/>
-      <c r="T66" s="2" t="inlineStr">
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="n"/>
+      <c r="U66" s="2" t="n"/>
+      <c r="V66" s="2" t="inlineStr">
         <is>
           <t>JH</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4516,36 +4516,19 @@
           <t>process context</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4575,33 +4558,33 @@
       <c r="I68" s="2" t="n"/>
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
+      <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Upper level</t>
-        </is>
-      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Upper level</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="n"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="R68" s="2" t="n"/>
-      <c r="S68" s="2" t="n"/>
-      <c r="T68" s="2" t="inlineStr">
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="n"/>
+      <c r="U68" s="2" t="n"/>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="U68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V68" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
